--- a/ig/main/ValueSet-jdv-j378-region-om-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j378-region-om-finess.xlsx
@@ -8,12 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="90">
   <si>
     <t>Property</t>
   </si>
@@ -118,6 +120,171 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R30-RegionOM/FHIR/TRE-R30-RegionOM</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R30-RegionOM/FHIR/TRE-R30-RegionOM|20240628120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>Auvergne-Rhône-Alpes</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Bourgogne-Franche-Comté</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>Bretagne</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Centre-Val de Loire</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>Corse</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Grand Est</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Guadeloupe</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>Guyane</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Hauts-de-France</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>La Réunion</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Martinique</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Mayotte</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Normandie</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>Nouvelle-Aquitaine</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>Occitanie</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Pays de la Loire</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>Provence-Alpes-Côte d'Azur</t>
+  </si>
+  <si>
+    <t>977</t>
+  </si>
+  <si>
+    <t>Saint-Barthélemy</t>
+  </si>
+  <si>
+    <t>978</t>
+  </si>
+  <si>
+    <t>Saint-Martin</t>
+  </si>
+  <si>
+    <t>975</t>
+  </si>
+  <si>
+    <t>Saint-Pierre-et-Miquelon</t>
+  </si>
+  <si>
+    <t>986</t>
+  </si>
+  <si>
+    <t>Wallis-et-Futuna</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Île-de-France</t>
   </si>
 </sst>
 </file>
@@ -429,4 +596,533 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>